--- a/public/templates/forms/A-094-PrivilegeReviewRecords-FORM.xlsx
+++ b/public/templates/forms/A-094-PrivilegeReviewRecords-FORM.xlsx
@@ -586,7 +586,7 @@
       <c r="E6" s="17" t="n"/>
       <c r="F6" s="16" t="n"/>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7" ht="78" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Review period / Scope</t>
@@ -595,7 +595,7 @@
       <c r="B7" s="16" t="n"/>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Covers periodic least-privilege reviews of [systems / account sets] against the RBAC Documentation and Access Entitlement Matrix.  Review cadence: [quarterly].  Reviewer (role): [role].</t>
+          <t>Covers periodic least-privilege / entitlement-conformance reviews of [systems / account sets], covering every account type including privileged, against the RBAC Documentation and Access Entitlement Matrix. Privileged-account usage and session-monitoring reviews are recorded in the Privileged Access Review Records; account certification in the Periodic Account Review / Certification Records.  Review cadence: [quarterly].  Reviewer (role): [role].</t>
         </is>
       </c>
       <c r="D7" s="17" t="n"/>
@@ -988,10 +988,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="43.5" customHeight="1">
+    <row r="2" ht="43.5" customHeight="19">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>How to use this template (delete this sheet’s notes before publishing): record each least-privilege review against the RBAC Documentation (A-093) and Access Entitlement Matrix (A-035). This record covers least-privilege / RBAC reviews (category 2.D); privileged-account reviews are recorded in the Privileged Access Review Records, and account certification in the Periodic Account Review / Certification Records.</t>
+          <t>How to use this template (delete this sheet’s notes before publishing): record each least-privilege / entitlement-conformance review against the RBAC Documentation and Access Entitlement Matrix. This record covers entitlement conformance for every account type, privileged included (category 2.D). Privileged-account usage (creep) and session-monitoring reviews are recorded in the Privileged Access Review Records (category 2.E); account certification in the Periodic Account Review / Certification Records.</t>
         </is>
       </c>
     </row>

--- a/public/templates/forms/A-094-PrivilegeReviewRecords-FORM.xlsx
+++ b/public/templates/forms/A-094-PrivilegeReviewRecords-FORM.xlsx
@@ -3,12 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="23380" windowHeight="21660" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="23380" windowHeight="21660" tabRatio="500" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Log" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Log!$11:$11</definedName>
+  </definedNames>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -609,7 +612,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
+    <row r="10" ht="34.7" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>« One row per review cycle. Record what was reviewed, against the RBAC Documentation and Access Entitlement Matrix, and what rights were confirmed, revoked, or changed. Mirror open items into the Risk / Finding Register. »</t>
@@ -922,7 +925,7 @@
       <c r="E46" s="11" t="n"/>
       <c r="F46" s="11" t="n"/>
     </row>
-    <row r="48" ht="30" customHeight="1">
+    <row r="48" ht="34.7" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Drafter’s note (internal, delete before publishing): list any [BRACKETED] field that could not be resolved from project context, and any decision needing confirmation.</t>
@@ -962,7 +965,7 @@
     <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -988,14 +991,14 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="43.5" customHeight="19">
+    <row r="2" ht="66.4" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>How to use this template (delete this sheet’s notes before publishing): record each least-privilege / entitlement-conformance review against the RBAC Documentation and Access Entitlement Matrix. This record covers entitlement conformance for every account type, privileged included (category 2.D). Privileged-account usage (creep) and session-monitoring reviews are recorded in the Privileged Access Review Records (category 2.E); account certification in the Periodic Account Review / Certification Records.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="29.75" customHeight="1">
+    <row r="3" ht="34.7" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Placeholder key:  [BRACKETED] = fill in   ·   « » = guidance to delete.  Classification, findings, sign-off, retention and revision history live on the Log tab.</t>
@@ -1053,7 +1056,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
+    <row r="8" ht="34.7" customHeight="1">
       <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Review date &amp; scope</t>
@@ -1075,7 +1078,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
+    <row r="9" ht="34.7" customHeight="1">
       <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Reviewer (role)</t>
@@ -1097,7 +1100,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
+    <row r="10" ht="50.5" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
         <is>
           <t>Accounts / roles reviewed</t>
@@ -1141,7 +1144,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
+    <row r="12" ht="34.7" customHeight="1">
       <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Follow-up</t>
@@ -1238,6 +1241,6 @@
     <mergeCell ref="B19:D19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>